--- a/new-stats/sepsi-osk-sftantu-gheorghe.xlsx
+++ b/new-stats/sepsi-osk-sftantu-gheorghe.xlsx
@@ -569,22 +569,62 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sepsi Sf. Gheorghe</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>U. Cluj</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M3" t="n">
+        <v>13</v>
+      </c>
+      <c r="N3" t="n">
+        <v>14</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>

--- a/new-stats/sepsi-osk-sftantu-gheorghe.xlsx
+++ b/new-stats/sepsi-osk-sftantu-gheorghe.xlsx
@@ -627,22 +627,62 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Corvinul</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sepsi Sf. Gheorghe</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M4" t="n">
+        <v>13</v>
+      </c>
+      <c r="N4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>

--- a/new-stats/sepsi-osk-sftantu-gheorghe.xlsx
+++ b/new-stats/sepsi-osk-sftantu-gheorghe.xlsx
@@ -685,40 +685,120 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sepsi Sf. Gheorghe</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FCSB</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>14</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Csikszereda M. Ciuc</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sepsi Sf. Gheorghe</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
